--- a/Git_TP.xlsx
+++ b/Git_TP.xlsx
@@ -5,14 +5,759 @@
   <x:bookViews>
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
-  <x:sheets/>
+  <x:sheets>
+    <x:sheet name="SheetMap" sheetId="2" r:id="rId2"/>
+    <x:sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+  </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+  <x:si>
+    <x:t>ExcelSheet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SheetName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sheet1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Git_TS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TestScenarioID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TestCaseID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Precondition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TestData</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Steps</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserAction</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExpectedResult</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approved/Rejected</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ReasonToReject</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsModified/Added</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TestScenario_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TestScenario_1.TestCase_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>New New Registration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User Needs to Login to Ezovion Platform, from the browser with correct credentials</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the Registration button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click on the Registration button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the New Registration button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click on the New Registration button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Please select a value for required field Title .</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Title field. Otherwise "Error: You must select a value" message will be displayed.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Title field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valid value for required field First Name .</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  First Name field and it should not be empty. Otherwise "Error: You must enter a value" message will be displayed.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the First Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Please select a value for required field Gender .</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Gender field. Otherwise "Error: You must select a value" message will be displayed.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Gender field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valid value for required field Mobile .</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Mobile field and it should not be empty. Otherwise "Error: You must enter a value" message will be displayed.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Mobile field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Middle Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Middle Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Last Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Last Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  MM/DD/YYYY field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the MM/DD/YYYY field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Years field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Years field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Months field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Months field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Days field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Days field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Birth Place field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Birth Place field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Birth Time field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Birth Time field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Mobile field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Mobile field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Alternate Mobile field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Alternate Mobile field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Alternate Mobile field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Alternate Mobile field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Office Phone field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Office Phone field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Email field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Email field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Relation field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Relation field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Relation Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Relation Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the Auto-fill Address from Family Member checkbox field to select it.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click value for the Auto-fill Address from Family Member checkbox field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Door No/ Street Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Door No/ Street Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Address Line1 field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Address Line1 field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Address Line2 field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Address Line2 field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   City / Town field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the City / Town field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Pincode field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Pincode field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Area field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Area field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   District field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the District field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   State field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the State field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Country field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Country field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Region field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Region field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Guardian Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Guardian Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Relationship field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Relationship field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Mobile Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Mobile Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Mobile Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Mobile Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Landline field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Landline field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Address field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Address field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Other Contact Person field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Other Contact Person field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Referral field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Referral field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   How do you know about us field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the How do you know about us field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Religion field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Religion field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Citizenship field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Citizenship field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Nationality field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Nationality field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Marital Status field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Marital Status field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Language field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Language field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Occupation field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Occupation field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Special Care field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Special Care field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Special Courtesy field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Special Courtesy field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select a value from   Study Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to select a value for the Study Name field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Passport Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Passport Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  National ID Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the National ID Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Driving Licence No. field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Driving Licence No. field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Refugee No field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Refugee No field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  PAN Card field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the PAN Card field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Aadhar Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Aadhar Number field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  PhilHealth PIN field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the PhilHealth PIN field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  FRRO No. field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the FRRO No. field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  ABHA No. field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the ABHA No. field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  ABHA Address field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the ABHA Address field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Visa Issue Date field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Visa Issue Date field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Visa Validity field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Visa Validity field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Date Of Entry field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Date Of Entry field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Port of Entry field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Port of Entry field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Residential Address field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Residential Address field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Office / Work Address field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Office / Work Address field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Input a valid value in the  Remarks field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to input a value for the Remarks field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the deceasedFlag checkbox field to select it.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click value for the deceasedFlag checkbox field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the Is Active checkbox field to select it.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click value for the Is Active checkbox field.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the Save button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click on the Save button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the Save and Make Appointment button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click on the Save and Make Appointment button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the Cancel button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click on the Cancel button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step 78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Click on the Reset button.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User should be able to click on the Reset button.</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20,7 +765,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="3">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -28,16 +773,38 @@
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:u val="single"/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color theme="10"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0000FF"/>
+        <x:bgColor rgb="FF0000FF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="4">
     <x:border diagonalUp="0" diagonalDown="0">
       <x:left style="none">
         <x:color rgb="FF000000"/>
@@ -55,14 +822,93 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -71,6 +917,26 @@
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K80" totalsRowShown="0">
+  <x:autoFilter ref="A1:K80"/>
+  <x:tableColumns count="11">
+    <x:tableColumn id="1" name="TestScenarioID"/>
+    <x:tableColumn id="2" name="TestCaseID"/>
+    <x:tableColumn id="3" name="Description"/>
+    <x:tableColumn id="4" name="Precondition"/>
+    <x:tableColumn id="5" name="TestData"/>
+    <x:tableColumn id="6" name="Steps"/>
+    <x:tableColumn id="7" name="UserAction"/>
+    <x:tableColumn id="8" name="ExpectedResult"/>
+    <x:tableColumn id="9" name="Approved/Rejected"/>
+    <x:tableColumn id="10" name="ReasonToReject"/>
+    <x:tableColumn id="11" name="IsModified/Added"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,4 +1220,1622 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B2"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.700625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.410625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:hyperlinks>
+    <x:hyperlink ref="A2" location="'Sheet1'!A1" display="Sheet1"/>
+  </x:hyperlinks>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K80"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15.980625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26.270625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22.700625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="75.700624999999988" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="44.840625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.410625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="125.410625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="86.700624999999988" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20.410625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16.980625" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18.980625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:11">
+      <x:c r="A1" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J1" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K1" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
+      <x:c r="A2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s"/>
+      <x:c r="F2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s"/>
+      <x:c r="J2" s="0" t="s"/>
+      <x:c r="K2" s="0" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:11">
+      <x:c r="A3" s="0" t="s"/>
+      <x:c r="B3" s="0" t="s"/>
+      <x:c r="C3" s="0" t="s"/>
+      <x:c r="D3" s="0" t="s"/>
+      <x:c r="E3" s="0" t="s"/>
+      <x:c r="F3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s"/>
+      <x:c r="J3" s="0" t="s"/>
+      <x:c r="K3" s="0" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="0" t="s"/>
+      <x:c r="B4" s="0" t="s"/>
+      <x:c r="C4" s="0" t="s"/>
+      <x:c r="D4" s="0" t="s"/>
+      <x:c r="E4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s"/>
+      <x:c r="J4" s="0" t="s"/>
+      <x:c r="K4" s="0" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="0" t="s"/>
+      <x:c r="B5" s="0" t="s"/>
+      <x:c r="C5" s="0" t="s"/>
+      <x:c r="D5" s="0" t="s"/>
+      <x:c r="E5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s"/>
+      <x:c r="J5" s="0" t="s"/>
+      <x:c r="K5" s="0" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:11">
+      <x:c r="A6" s="0" t="s"/>
+      <x:c r="B6" s="0" t="s"/>
+      <x:c r="C6" s="0" t="s"/>
+      <x:c r="D6" s="0" t="s"/>
+      <x:c r="E6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s"/>
+      <x:c r="J6" s="0" t="s"/>
+      <x:c r="K6" s="0" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="0" t="s"/>
+      <x:c r="B7" s="0" t="s"/>
+      <x:c r="C7" s="0" t="s"/>
+      <x:c r="D7" s="0" t="s"/>
+      <x:c r="E7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s"/>
+      <x:c r="J7" s="0" t="s"/>
+      <x:c r="K7" s="0" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="0" t="s"/>
+      <x:c r="B8" s="0" t="s"/>
+      <x:c r="C8" s="0" t="s"/>
+      <x:c r="D8" s="0" t="s"/>
+      <x:c r="E8" s="0" t="s"/>
+      <x:c r="F8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s"/>
+      <x:c r="J8" s="0" t="s"/>
+      <x:c r="K8" s="0" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:11">
+      <x:c r="A9" s="0" t="s"/>
+      <x:c r="B9" s="0" t="s"/>
+      <x:c r="C9" s="0" t="s"/>
+      <x:c r="D9" s="0" t="s"/>
+      <x:c r="E9" s="0" t="s"/>
+      <x:c r="F9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s"/>
+      <x:c r="J9" s="0" t="s"/>
+      <x:c r="K9" s="0" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:11">
+      <x:c r="A10" s="0" t="s"/>
+      <x:c r="B10" s="0" t="s"/>
+      <x:c r="C10" s="0" t="s"/>
+      <x:c r="D10" s="0" t="s"/>
+      <x:c r="E10" s="0" t="s"/>
+      <x:c r="F10" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s"/>
+      <x:c r="J10" s="0" t="s"/>
+      <x:c r="K10" s="0" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="0" t="s"/>
+      <x:c r="B11" s="0" t="s"/>
+      <x:c r="C11" s="0" t="s"/>
+      <x:c r="D11" s="0" t="s"/>
+      <x:c r="E11" s="0" t="s"/>
+      <x:c r="F11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s"/>
+      <x:c r="J11" s="0" t="s"/>
+      <x:c r="K11" s="0" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="0" t="s"/>
+      <x:c r="B12" s="0" t="s"/>
+      <x:c r="C12" s="0" t="s"/>
+      <x:c r="D12" s="0" t="s"/>
+      <x:c r="E12" s="0" t="s"/>
+      <x:c r="F12" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s"/>
+      <x:c r="J12" s="0" t="s"/>
+      <x:c r="K12" s="0" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="0" t="s"/>
+      <x:c r="B13" s="0" t="s"/>
+      <x:c r="C13" s="0" t="s"/>
+      <x:c r="D13" s="0" t="s"/>
+      <x:c r="E13" s="0" t="s"/>
+      <x:c r="F13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s"/>
+      <x:c r="J13" s="0" t="s"/>
+      <x:c r="K13" s="0" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="0" t="s"/>
+      <x:c r="B14" s="0" t="s"/>
+      <x:c r="C14" s="0" t="s"/>
+      <x:c r="D14" s="0" t="s"/>
+      <x:c r="E14" s="0" t="s"/>
+      <x:c r="F14" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s"/>
+      <x:c r="J14" s="0" t="s"/>
+      <x:c r="K14" s="0" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:11">
+      <x:c r="A15" s="0" t="s"/>
+      <x:c r="B15" s="0" t="s"/>
+      <x:c r="C15" s="0" t="s"/>
+      <x:c r="D15" s="0" t="s"/>
+      <x:c r="E15" s="0" t="s"/>
+      <x:c r="F15" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s"/>
+      <x:c r="J15" s="0" t="s"/>
+      <x:c r="K15" s="0" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="0" t="s"/>
+      <x:c r="B16" s="0" t="s"/>
+      <x:c r="C16" s="0" t="s"/>
+      <x:c r="D16" s="0" t="s"/>
+      <x:c r="E16" s="0" t="s"/>
+      <x:c r="F16" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s"/>
+      <x:c r="J16" s="0" t="s"/>
+      <x:c r="K16" s="0" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="0" t="s"/>
+      <x:c r="B17" s="0" t="s"/>
+      <x:c r="C17" s="0" t="s"/>
+      <x:c r="D17" s="0" t="s"/>
+      <x:c r="E17" s="0" t="s"/>
+      <x:c r="F17" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s"/>
+      <x:c r="J17" s="0" t="s"/>
+      <x:c r="K17" s="0" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="0" t="s"/>
+      <x:c r="B18" s="0" t="s"/>
+      <x:c r="C18" s="0" t="s"/>
+      <x:c r="D18" s="0" t="s"/>
+      <x:c r="E18" s="0" t="s"/>
+      <x:c r="F18" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s"/>
+      <x:c r="J18" s="0" t="s"/>
+      <x:c r="K18" s="0" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="0" t="s"/>
+      <x:c r="B19" s="0" t="s"/>
+      <x:c r="C19" s="0" t="s"/>
+      <x:c r="D19" s="0" t="s"/>
+      <x:c r="E19" s="0" t="s"/>
+      <x:c r="F19" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s"/>
+      <x:c r="J19" s="0" t="s"/>
+      <x:c r="K19" s="0" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="0" t="s"/>
+      <x:c r="B20" s="0" t="s"/>
+      <x:c r="C20" s="0" t="s"/>
+      <x:c r="D20" s="0" t="s"/>
+      <x:c r="E20" s="0" t="s"/>
+      <x:c r="F20" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s"/>
+      <x:c r="J20" s="0" t="s"/>
+      <x:c r="K20" s="0" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:11">
+      <x:c r="A21" s="0" t="s"/>
+      <x:c r="B21" s="0" t="s"/>
+      <x:c r="C21" s="0" t="s"/>
+      <x:c r="D21" s="0" t="s"/>
+      <x:c r="E21" s="0" t="s"/>
+      <x:c r="F21" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s"/>
+      <x:c r="J21" s="0" t="s"/>
+      <x:c r="K21" s="0" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="0" t="s"/>
+      <x:c r="B22" s="0" t="s"/>
+      <x:c r="C22" s="0" t="s"/>
+      <x:c r="D22" s="0" t="s"/>
+      <x:c r="E22" s="0" t="s"/>
+      <x:c r="F22" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s"/>
+      <x:c r="J22" s="0" t="s"/>
+      <x:c r="K22" s="0" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:11">
+      <x:c r="A23" s="0" t="s"/>
+      <x:c r="B23" s="0" t="s"/>
+      <x:c r="C23" s="0" t="s"/>
+      <x:c r="D23" s="0" t="s"/>
+      <x:c r="E23" s="0" t="s"/>
+      <x:c r="F23" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s"/>
+      <x:c r="J23" s="0" t="s"/>
+      <x:c r="K23" s="0" t="s"/>
+    </x:row>
+    <x:row r="24" spans="1:11">
+      <x:c r="A24" s="0" t="s"/>
+      <x:c r="B24" s="0" t="s"/>
+      <x:c r="C24" s="0" t="s"/>
+      <x:c r="D24" s="0" t="s"/>
+      <x:c r="E24" s="0" t="s"/>
+      <x:c r="F24" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s"/>
+      <x:c r="J24" s="0" t="s"/>
+      <x:c r="K24" s="0" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:11">
+      <x:c r="A25" s="0" t="s"/>
+      <x:c r="B25" s="0" t="s"/>
+      <x:c r="C25" s="0" t="s"/>
+      <x:c r="D25" s="0" t="s"/>
+      <x:c r="E25" s="0" t="s"/>
+      <x:c r="F25" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s"/>
+      <x:c r="J25" s="0" t="s"/>
+      <x:c r="K25" s="0" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:11">
+      <x:c r="A26" s="0" t="s"/>
+      <x:c r="B26" s="0" t="s"/>
+      <x:c r="C26" s="0" t="s"/>
+      <x:c r="D26" s="0" t="s"/>
+      <x:c r="E26" s="0" t="s"/>
+      <x:c r="F26" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s"/>
+      <x:c r="J26" s="0" t="s"/>
+      <x:c r="K26" s="0" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:11">
+      <x:c r="A27" s="0" t="s"/>
+      <x:c r="B27" s="0" t="s"/>
+      <x:c r="C27" s="0" t="s"/>
+      <x:c r="D27" s="0" t="s"/>
+      <x:c r="E27" s="0" t="s"/>
+      <x:c r="F27" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s"/>
+      <x:c r="J27" s="0" t="s"/>
+      <x:c r="K27" s="0" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:11">
+      <x:c r="A28" s="0" t="s"/>
+      <x:c r="B28" s="0" t="s"/>
+      <x:c r="C28" s="0" t="s"/>
+      <x:c r="D28" s="0" t="s"/>
+      <x:c r="E28" s="0" t="s"/>
+      <x:c r="F28" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s"/>
+      <x:c r="J28" s="0" t="s"/>
+      <x:c r="K28" s="0" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:11">
+      <x:c r="A29" s="0" t="s"/>
+      <x:c r="B29" s="0" t="s"/>
+      <x:c r="C29" s="0" t="s"/>
+      <x:c r="D29" s="0" t="s"/>
+      <x:c r="E29" s="0" t="s"/>
+      <x:c r="F29" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s"/>
+      <x:c r="J29" s="0" t="s"/>
+      <x:c r="K29" s="0" t="s"/>
+    </x:row>
+    <x:row r="30" spans="1:11">
+      <x:c r="A30" s="0" t="s"/>
+      <x:c r="B30" s="0" t="s"/>
+      <x:c r="C30" s="0" t="s"/>
+      <x:c r="D30" s="0" t="s"/>
+      <x:c r="E30" s="0" t="s"/>
+      <x:c r="F30" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s"/>
+      <x:c r="J30" s="0" t="s"/>
+      <x:c r="K30" s="0" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:11">
+      <x:c r="A31" s="0" t="s"/>
+      <x:c r="B31" s="0" t="s"/>
+      <x:c r="C31" s="0" t="s"/>
+      <x:c r="D31" s="0" t="s"/>
+      <x:c r="E31" s="0" t="s"/>
+      <x:c r="F31" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s"/>
+      <x:c r="J31" s="0" t="s"/>
+      <x:c r="K31" s="0" t="s"/>
+    </x:row>
+    <x:row r="32" spans="1:11">
+      <x:c r="A32" s="0" t="s"/>
+      <x:c r="B32" s="0" t="s"/>
+      <x:c r="C32" s="0" t="s"/>
+      <x:c r="D32" s="0" t="s"/>
+      <x:c r="E32" s="0" t="s"/>
+      <x:c r="F32" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s"/>
+      <x:c r="J32" s="0" t="s"/>
+      <x:c r="K32" s="0" t="s"/>
+    </x:row>
+    <x:row r="33" spans="1:11">
+      <x:c r="A33" s="0" t="s"/>
+      <x:c r="B33" s="0" t="s"/>
+      <x:c r="C33" s="0" t="s"/>
+      <x:c r="D33" s="0" t="s"/>
+      <x:c r="E33" s="0" t="s"/>
+      <x:c r="F33" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s"/>
+      <x:c r="J33" s="0" t="s"/>
+      <x:c r="K33" s="0" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:11">
+      <x:c r="A34" s="0" t="s"/>
+      <x:c r="B34" s="0" t="s"/>
+      <x:c r="C34" s="0" t="s"/>
+      <x:c r="D34" s="0" t="s"/>
+      <x:c r="E34" s="0" t="s"/>
+      <x:c r="F34" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s"/>
+      <x:c r="J34" s="0" t="s"/>
+      <x:c r="K34" s="0" t="s"/>
+    </x:row>
+    <x:row r="35" spans="1:11">
+      <x:c r="A35" s="0" t="s"/>
+      <x:c r="B35" s="0" t="s"/>
+      <x:c r="C35" s="0" t="s"/>
+      <x:c r="D35" s="0" t="s"/>
+      <x:c r="E35" s="0" t="s"/>
+      <x:c r="F35" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s"/>
+      <x:c r="J35" s="0" t="s"/>
+      <x:c r="K35" s="0" t="s"/>
+    </x:row>
+    <x:row r="36" spans="1:11">
+      <x:c r="A36" s="0" t="s"/>
+      <x:c r="B36" s="0" t="s"/>
+      <x:c r="C36" s="0" t="s"/>
+      <x:c r="D36" s="0" t="s"/>
+      <x:c r="E36" s="0" t="s"/>
+      <x:c r="F36" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s"/>
+      <x:c r="J36" s="0" t="s"/>
+      <x:c r="K36" s="0" t="s"/>
+    </x:row>
+    <x:row r="37" spans="1:11">
+      <x:c r="A37" s="0" t="s"/>
+      <x:c r="B37" s="0" t="s"/>
+      <x:c r="C37" s="0" t="s"/>
+      <x:c r="D37" s="0" t="s"/>
+      <x:c r="E37" s="0" t="s"/>
+      <x:c r="F37" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s"/>
+      <x:c r="J37" s="0" t="s"/>
+      <x:c r="K37" s="0" t="s"/>
+    </x:row>
+    <x:row r="38" spans="1:11">
+      <x:c r="A38" s="0" t="s"/>
+      <x:c r="B38" s="0" t="s"/>
+      <x:c r="C38" s="0" t="s"/>
+      <x:c r="D38" s="0" t="s"/>
+      <x:c r="E38" s="0" t="s"/>
+      <x:c r="F38" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s"/>
+      <x:c r="J38" s="0" t="s"/>
+      <x:c r="K38" s="0" t="s"/>
+    </x:row>
+    <x:row r="39" spans="1:11">
+      <x:c r="A39" s="0" t="s"/>
+      <x:c r="B39" s="0" t="s"/>
+      <x:c r="C39" s="0" t="s"/>
+      <x:c r="D39" s="0" t="s"/>
+      <x:c r="E39" s="0" t="s"/>
+      <x:c r="F39" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s"/>
+      <x:c r="J39" s="0" t="s"/>
+      <x:c r="K39" s="0" t="s"/>
+    </x:row>
+    <x:row r="40" spans="1:11">
+      <x:c r="A40" s="0" t="s"/>
+      <x:c r="B40" s="0" t="s"/>
+      <x:c r="C40" s="0" t="s"/>
+      <x:c r="D40" s="0" t="s"/>
+      <x:c r="E40" s="0" t="s"/>
+      <x:c r="F40" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s"/>
+      <x:c r="J40" s="0" t="s"/>
+      <x:c r="K40" s="0" t="s"/>
+    </x:row>
+    <x:row r="41" spans="1:11">
+      <x:c r="A41" s="0" t="s"/>
+      <x:c r="B41" s="0" t="s"/>
+      <x:c r="C41" s="0" t="s"/>
+      <x:c r="D41" s="0" t="s"/>
+      <x:c r="E41" s="0" t="s"/>
+      <x:c r="F41" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s"/>
+      <x:c r="J41" s="0" t="s"/>
+      <x:c r="K41" s="0" t="s"/>
+    </x:row>
+    <x:row r="42" spans="1:11">
+      <x:c r="A42" s="0" t="s"/>
+      <x:c r="B42" s="0" t="s"/>
+      <x:c r="C42" s="0" t="s"/>
+      <x:c r="D42" s="0" t="s"/>
+      <x:c r="E42" s="0" t="s"/>
+      <x:c r="F42" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s"/>
+      <x:c r="J42" s="0" t="s"/>
+      <x:c r="K42" s="0" t="s"/>
+    </x:row>
+    <x:row r="43" spans="1:11">
+      <x:c r="A43" s="0" t="s"/>
+      <x:c r="B43" s="0" t="s"/>
+      <x:c r="C43" s="0" t="s"/>
+      <x:c r="D43" s="0" t="s"/>
+      <x:c r="E43" s="0" t="s"/>
+      <x:c r="F43" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s"/>
+      <x:c r="J43" s="0" t="s"/>
+      <x:c r="K43" s="0" t="s"/>
+    </x:row>
+    <x:row r="44" spans="1:11">
+      <x:c r="A44" s="0" t="s"/>
+      <x:c r="B44" s="0" t="s"/>
+      <x:c r="C44" s="0" t="s"/>
+      <x:c r="D44" s="0" t="s"/>
+      <x:c r="E44" s="0" t="s"/>
+      <x:c r="F44" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s"/>
+      <x:c r="J44" s="0" t="s"/>
+      <x:c r="K44" s="0" t="s"/>
+    </x:row>
+    <x:row r="45" spans="1:11">
+      <x:c r="A45" s="0" t="s"/>
+      <x:c r="B45" s="0" t="s"/>
+      <x:c r="C45" s="0" t="s"/>
+      <x:c r="D45" s="0" t="s"/>
+      <x:c r="E45" s="0" t="s"/>
+      <x:c r="F45" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s"/>
+      <x:c r="J45" s="0" t="s"/>
+      <x:c r="K45" s="0" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:11">
+      <x:c r="A46" s="0" t="s"/>
+      <x:c r="B46" s="0" t="s"/>
+      <x:c r="C46" s="0" t="s"/>
+      <x:c r="D46" s="0" t="s"/>
+      <x:c r="E46" s="0" t="s"/>
+      <x:c r="F46" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s"/>
+      <x:c r="J46" s="0" t="s"/>
+      <x:c r="K46" s="0" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:11">
+      <x:c r="A47" s="0" t="s"/>
+      <x:c r="B47" s="0" t="s"/>
+      <x:c r="C47" s="0" t="s"/>
+      <x:c r="D47" s="0" t="s"/>
+      <x:c r="E47" s="0" t="s"/>
+      <x:c r="F47" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s"/>
+      <x:c r="J47" s="0" t="s"/>
+      <x:c r="K47" s="0" t="s"/>
+    </x:row>
+    <x:row r="48" spans="1:11">
+      <x:c r="A48" s="0" t="s"/>
+      <x:c r="B48" s="0" t="s"/>
+      <x:c r="C48" s="0" t="s"/>
+      <x:c r="D48" s="0" t="s"/>
+      <x:c r="E48" s="0" t="s"/>
+      <x:c r="F48" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s"/>
+      <x:c r="J48" s="0" t="s"/>
+      <x:c r="K48" s="0" t="s"/>
+    </x:row>
+    <x:row r="49" spans="1:11">
+      <x:c r="A49" s="0" t="s"/>
+      <x:c r="B49" s="0" t="s"/>
+      <x:c r="C49" s="0" t="s"/>
+      <x:c r="D49" s="0" t="s"/>
+      <x:c r="E49" s="0" t="s"/>
+      <x:c r="F49" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s"/>
+      <x:c r="J49" s="0" t="s"/>
+      <x:c r="K49" s="0" t="s"/>
+    </x:row>
+    <x:row r="50" spans="1:11">
+      <x:c r="A50" s="0" t="s"/>
+      <x:c r="B50" s="0" t="s"/>
+      <x:c r="C50" s="0" t="s"/>
+      <x:c r="D50" s="0" t="s"/>
+      <x:c r="E50" s="0" t="s"/>
+      <x:c r="F50" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s"/>
+      <x:c r="J50" s="0" t="s"/>
+      <x:c r="K50" s="0" t="s"/>
+    </x:row>
+    <x:row r="51" spans="1:11">
+      <x:c r="A51" s="0" t="s"/>
+      <x:c r="B51" s="0" t="s"/>
+      <x:c r="C51" s="0" t="s"/>
+      <x:c r="D51" s="0" t="s"/>
+      <x:c r="E51" s="0" t="s"/>
+      <x:c r="F51" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s"/>
+      <x:c r="J51" s="0" t="s"/>
+      <x:c r="K51" s="0" t="s"/>
+    </x:row>
+    <x:row r="52" spans="1:11">
+      <x:c r="A52" s="0" t="s"/>
+      <x:c r="B52" s="0" t="s"/>
+      <x:c r="C52" s="0" t="s"/>
+      <x:c r="D52" s="0" t="s"/>
+      <x:c r="E52" s="0" t="s"/>
+      <x:c r="F52" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s"/>
+      <x:c r="J52" s="0" t="s"/>
+      <x:c r="K52" s="0" t="s"/>
+    </x:row>
+    <x:row r="53" spans="1:11">
+      <x:c r="A53" s="0" t="s"/>
+      <x:c r="B53" s="0" t="s"/>
+      <x:c r="C53" s="0" t="s"/>
+      <x:c r="D53" s="0" t="s"/>
+      <x:c r="E53" s="0" t="s"/>
+      <x:c r="F53" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s"/>
+      <x:c r="J53" s="0" t="s"/>
+      <x:c r="K53" s="0" t="s"/>
+    </x:row>
+    <x:row r="54" spans="1:11">
+      <x:c r="A54" s="0" t="s"/>
+      <x:c r="B54" s="0" t="s"/>
+      <x:c r="C54" s="0" t="s"/>
+      <x:c r="D54" s="0" t="s"/>
+      <x:c r="E54" s="0" t="s"/>
+      <x:c r="F54" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s"/>
+      <x:c r="J54" s="0" t="s"/>
+      <x:c r="K54" s="0" t="s"/>
+    </x:row>
+    <x:row r="55" spans="1:11">
+      <x:c r="A55" s="0" t="s"/>
+      <x:c r="B55" s="0" t="s"/>
+      <x:c r="C55" s="0" t="s"/>
+      <x:c r="D55" s="0" t="s"/>
+      <x:c r="E55" s="0" t="s"/>
+      <x:c r="F55" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="I55" s="0" t="s"/>
+      <x:c r="J55" s="0" t="s"/>
+      <x:c r="K55" s="0" t="s"/>
+    </x:row>
+    <x:row r="56" spans="1:11">
+      <x:c r="A56" s="0" t="s"/>
+      <x:c r="B56" s="0" t="s"/>
+      <x:c r="C56" s="0" t="s"/>
+      <x:c r="D56" s="0" t="s"/>
+      <x:c r="E56" s="0" t="s"/>
+      <x:c r="F56" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="I56" s="0" t="s"/>
+      <x:c r="J56" s="0" t="s"/>
+      <x:c r="K56" s="0" t="s"/>
+    </x:row>
+    <x:row r="57" spans="1:11">
+      <x:c r="A57" s="0" t="s"/>
+      <x:c r="B57" s="0" t="s"/>
+      <x:c r="C57" s="0" t="s"/>
+      <x:c r="D57" s="0" t="s"/>
+      <x:c r="E57" s="0" t="s"/>
+      <x:c r="F57" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="I57" s="0" t="s"/>
+      <x:c r="J57" s="0" t="s"/>
+      <x:c r="K57" s="0" t="s"/>
+    </x:row>
+    <x:row r="58" spans="1:11">
+      <x:c r="A58" s="0" t="s"/>
+      <x:c r="B58" s="0" t="s"/>
+      <x:c r="C58" s="0" t="s"/>
+      <x:c r="D58" s="0" t="s"/>
+      <x:c r="E58" s="0" t="s"/>
+      <x:c r="F58" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="I58" s="0" t="s"/>
+      <x:c r="J58" s="0" t="s"/>
+      <x:c r="K58" s="0" t="s"/>
+    </x:row>
+    <x:row r="59" spans="1:11">
+      <x:c r="A59" s="0" t="s"/>
+      <x:c r="B59" s="0" t="s"/>
+      <x:c r="C59" s="0" t="s"/>
+      <x:c r="D59" s="0" t="s"/>
+      <x:c r="E59" s="0" t="s"/>
+      <x:c r="F59" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="I59" s="0" t="s"/>
+      <x:c r="J59" s="0" t="s"/>
+      <x:c r="K59" s="0" t="s"/>
+    </x:row>
+    <x:row r="60" spans="1:11">
+      <x:c r="A60" s="0" t="s"/>
+      <x:c r="B60" s="0" t="s"/>
+      <x:c r="C60" s="0" t="s"/>
+      <x:c r="D60" s="0" t="s"/>
+      <x:c r="E60" s="0" t="s"/>
+      <x:c r="F60" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s"/>
+      <x:c r="J60" s="0" t="s"/>
+      <x:c r="K60" s="0" t="s"/>
+    </x:row>
+    <x:row r="61" spans="1:11">
+      <x:c r="A61" s="0" t="s"/>
+      <x:c r="B61" s="0" t="s"/>
+      <x:c r="C61" s="0" t="s"/>
+      <x:c r="D61" s="0" t="s"/>
+      <x:c r="E61" s="0" t="s"/>
+      <x:c r="F61" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="I61" s="0" t="s"/>
+      <x:c r="J61" s="0" t="s"/>
+      <x:c r="K61" s="0" t="s"/>
+    </x:row>
+    <x:row r="62" spans="1:11">
+      <x:c r="A62" s="0" t="s"/>
+      <x:c r="B62" s="0" t="s"/>
+      <x:c r="C62" s="0" t="s"/>
+      <x:c r="D62" s="0" t="s"/>
+      <x:c r="E62" s="0" t="s"/>
+      <x:c r="F62" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="I62" s="0" t="s"/>
+      <x:c r="J62" s="0" t="s"/>
+      <x:c r="K62" s="0" t="s"/>
+    </x:row>
+    <x:row r="63" spans="1:11">
+      <x:c r="A63" s="0" t="s"/>
+      <x:c r="B63" s="0" t="s"/>
+      <x:c r="C63" s="0" t="s"/>
+      <x:c r="D63" s="0" t="s"/>
+      <x:c r="E63" s="0" t="s"/>
+      <x:c r="F63" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s"/>
+      <x:c r="J63" s="0" t="s"/>
+      <x:c r="K63" s="0" t="s"/>
+    </x:row>
+    <x:row r="64" spans="1:11">
+      <x:c r="A64" s="0" t="s"/>
+      <x:c r="B64" s="0" t="s"/>
+      <x:c r="C64" s="0" t="s"/>
+      <x:c r="D64" s="0" t="s"/>
+      <x:c r="E64" s="0" t="s"/>
+      <x:c r="F64" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s"/>
+      <x:c r="J64" s="0" t="s"/>
+      <x:c r="K64" s="0" t="s"/>
+    </x:row>
+    <x:row r="65" spans="1:11">
+      <x:c r="A65" s="0" t="s"/>
+      <x:c r="B65" s="0" t="s"/>
+      <x:c r="C65" s="0" t="s"/>
+      <x:c r="D65" s="0" t="s"/>
+      <x:c r="E65" s="0" t="s"/>
+      <x:c r="F65" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H65" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="I65" s="0" t="s"/>
+      <x:c r="J65" s="0" t="s"/>
+      <x:c r="K65" s="0" t="s"/>
+    </x:row>
+    <x:row r="66" spans="1:11">
+      <x:c r="A66" s="0" t="s"/>
+      <x:c r="B66" s="0" t="s"/>
+      <x:c r="C66" s="0" t="s"/>
+      <x:c r="D66" s="0" t="s"/>
+      <x:c r="E66" s="0" t="s"/>
+      <x:c r="F66" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H66" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="I66" s="0" t="s"/>
+      <x:c r="J66" s="0" t="s"/>
+      <x:c r="K66" s="0" t="s"/>
+    </x:row>
+    <x:row r="67" spans="1:11">
+      <x:c r="A67" s="0" t="s"/>
+      <x:c r="B67" s="0" t="s"/>
+      <x:c r="C67" s="0" t="s"/>
+      <x:c r="D67" s="0" t="s"/>
+      <x:c r="E67" s="0" t="s"/>
+      <x:c r="F67" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G67" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H67" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="I67" s="0" t="s"/>
+      <x:c r="J67" s="0" t="s"/>
+      <x:c r="K67" s="0" t="s"/>
+    </x:row>
+    <x:row r="68" spans="1:11">
+      <x:c r="A68" s="0" t="s"/>
+      <x:c r="B68" s="0" t="s"/>
+      <x:c r="C68" s="0" t="s"/>
+      <x:c r="D68" s="0" t="s"/>
+      <x:c r="E68" s="0" t="s"/>
+      <x:c r="F68" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G68" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H68" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="I68" s="0" t="s"/>
+      <x:c r="J68" s="0" t="s"/>
+      <x:c r="K68" s="0" t="s"/>
+    </x:row>
+    <x:row r="69" spans="1:11">
+      <x:c r="A69" s="0" t="s"/>
+      <x:c r="B69" s="0" t="s"/>
+      <x:c r="C69" s="0" t="s"/>
+      <x:c r="D69" s="0" t="s"/>
+      <x:c r="E69" s="0" t="s"/>
+      <x:c r="F69" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G69" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H69" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s"/>
+      <x:c r="J69" s="0" t="s"/>
+      <x:c r="K69" s="0" t="s"/>
+    </x:row>
+    <x:row r="70" spans="1:11">
+      <x:c r="A70" s="0" t="s"/>
+      <x:c r="B70" s="0" t="s"/>
+      <x:c r="C70" s="0" t="s"/>
+      <x:c r="D70" s="0" t="s"/>
+      <x:c r="E70" s="0" t="s"/>
+      <x:c r="F70" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G70" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="H70" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="I70" s="0" t="s"/>
+      <x:c r="J70" s="0" t="s"/>
+      <x:c r="K70" s="0" t="s"/>
+    </x:row>
+    <x:row r="71" spans="1:11">
+      <x:c r="A71" s="0" t="s"/>
+      <x:c r="B71" s="0" t="s"/>
+      <x:c r="C71" s="0" t="s"/>
+      <x:c r="D71" s="0" t="s"/>
+      <x:c r="E71" s="0" t="s"/>
+      <x:c r="F71" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G71" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H71" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="I71" s="0" t="s"/>
+      <x:c r="J71" s="0" t="s"/>
+      <x:c r="K71" s="0" t="s"/>
+    </x:row>
+    <x:row r="72" spans="1:11">
+      <x:c r="A72" s="0" t="s"/>
+      <x:c r="B72" s="0" t="s"/>
+      <x:c r="C72" s="0" t="s"/>
+      <x:c r="D72" s="0" t="s"/>
+      <x:c r="E72" s="0" t="s"/>
+      <x:c r="F72" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G72" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H72" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I72" s="0" t="s"/>
+      <x:c r="J72" s="0" t="s"/>
+      <x:c r="K72" s="0" t="s"/>
+    </x:row>
+    <x:row r="73" spans="1:11">
+      <x:c r="A73" s="0" t="s"/>
+      <x:c r="B73" s="0" t="s"/>
+      <x:c r="C73" s="0" t="s"/>
+      <x:c r="D73" s="0" t="s"/>
+      <x:c r="E73" s="0" t="s"/>
+      <x:c r="F73" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G73" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H73" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="I73" s="0" t="s"/>
+      <x:c r="J73" s="0" t="s"/>
+      <x:c r="K73" s="0" t="s"/>
+    </x:row>
+    <x:row r="74" spans="1:11">
+      <x:c r="A74" s="0" t="s"/>
+      <x:c r="B74" s="0" t="s"/>
+      <x:c r="C74" s="0" t="s"/>
+      <x:c r="D74" s="0" t="s"/>
+      <x:c r="E74" s="0" t="s"/>
+      <x:c r="F74" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G74" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H74" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="I74" s="0" t="s"/>
+      <x:c r="J74" s="0" t="s"/>
+      <x:c r="K74" s="0" t="s"/>
+    </x:row>
+    <x:row r="75" spans="1:11">
+      <x:c r="A75" s="0" t="s"/>
+      <x:c r="B75" s="0" t="s"/>
+      <x:c r="C75" s="0" t="s"/>
+      <x:c r="D75" s="0" t="s"/>
+      <x:c r="E75" s="0" t="s"/>
+      <x:c r="F75" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G75" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H75" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="I75" s="0" t="s"/>
+      <x:c r="J75" s="0" t="s"/>
+      <x:c r="K75" s="0" t="s"/>
+    </x:row>
+    <x:row r="76" spans="1:11">
+      <x:c r="A76" s="0" t="s"/>
+      <x:c r="B76" s="0" t="s"/>
+      <x:c r="C76" s="0" t="s"/>
+      <x:c r="D76" s="0" t="s"/>
+      <x:c r="E76" s="0" t="s"/>
+      <x:c r="F76" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G76" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="H76" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s"/>
+      <x:c r="J76" s="0" t="s"/>
+      <x:c r="K76" s="0" t="s"/>
+    </x:row>
+    <x:row r="77" spans="1:11">
+      <x:c r="A77" s="0" t="s"/>
+      <x:c r="B77" s="0" t="s"/>
+      <x:c r="C77" s="0" t="s"/>
+      <x:c r="D77" s="0" t="s"/>
+      <x:c r="E77" s="0" t="s"/>
+      <x:c r="F77" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G77" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H77" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="I77" s="0" t="s"/>
+      <x:c r="J77" s="0" t="s"/>
+      <x:c r="K77" s="0" t="s"/>
+    </x:row>
+    <x:row r="78" spans="1:11">
+      <x:c r="A78" s="0" t="s"/>
+      <x:c r="B78" s="0" t="s"/>
+      <x:c r="C78" s="0" t="s"/>
+      <x:c r="D78" s="0" t="s"/>
+      <x:c r="E78" s="0" t="s"/>
+      <x:c r="F78" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G78" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H78" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="I78" s="0" t="s"/>
+      <x:c r="J78" s="0" t="s"/>
+      <x:c r="K78" s="0" t="s"/>
+    </x:row>
+    <x:row r="79" spans="1:11">
+      <x:c r="A79" s="0" t="s"/>
+      <x:c r="B79" s="0" t="s"/>
+      <x:c r="C79" s="0" t="s"/>
+      <x:c r="D79" s="0" t="s"/>
+      <x:c r="E79" s="0" t="s"/>
+      <x:c r="F79" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G79" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H79" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="I79" s="0" t="s"/>
+      <x:c r="J79" s="0" t="s"/>
+      <x:c r="K79" s="0" t="s"/>
+    </x:row>
+    <x:row r="80" spans="1:11">
+      <x:c r="A80" s="0" t="s"/>
+      <x:c r="B80" s="0" t="s"/>
+      <x:c r="C80" s="0" t="s"/>
+      <x:c r="D80" s="0" t="s"/>
+      <x:c r="E80" s="0" t="s"/>
+      <x:c r="F80" s="0" t="s"/>
+      <x:c r="G80" s="0" t="s"/>
+      <x:c r="H80" s="0" t="s"/>
+      <x:c r="I80" s="0" t="s"/>
+      <x:c r="J80" s="0" t="s"/>
+      <x:c r="K80" s="0" t="s"/>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="1">
+    <x:tablePart r:id="rId6"/>
+  </x:tableParts>
+</x:worksheet>
 </file>